--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run2/epoch_80/per_file_predictions_epoch_80.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run2/epoch_80/per_file_predictions_epoch_80.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.8196,0.0273,0.0124,0.1098</t>
-  </si>
-  <si>
-    <t>0.1403,0.0054,0.0009,0.9581</t>
-  </si>
-  <si>
-    <t>0.8398,0.0015,0.0016,0.1969</t>
-  </si>
-  <si>
-    <t>0.0939,0.0021,0.0053,0.9637</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9939,0.0049,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9936,0.0040,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9625,0.0524,0.0012,0.0004</t>
-  </si>
-  <si>
-    <t>0.9956,0.0039,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9914,0.0088,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9980,0.0006,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.4341,0.1455,0.4926,0.0131</t>
-  </si>
-  <si>
-    <t>0.1658,0.0118,0.9178,0.0009</t>
-  </si>
-  <si>
-    <t>0.4974,0.0516,0.5138,0.0018</t>
-  </si>
-  <si>
-    <t>0.1517,0.1400,0.7067,0.0070</t>
-  </si>
-  <si>
-    <t>0.8684,0.0298,0.0920,0.0064</t>
-  </si>
-  <si>
-    <t>0.0074,0.9851,0.0140,0.0002</t>
-  </si>
-  <si>
-    <t>0.0117,0.9855,0.0043,0.0001</t>
-  </si>
-  <si>
-    <t>0.1169,0.8954,0.0111,0.0009</t>
-  </si>
-  <si>
-    <t>0.0319,0.9661,0.0064,0.0002</t>
-  </si>
-  <si>
-    <t>0.0044,0.9924,0.0042,0.0000</t>
-  </si>
-  <si>
-    <t>0.5279,0.0336,0.4969,0.0320</t>
-  </si>
-  <si>
-    <t>0.5271,0.0228,0.4549,0.0340</t>
-  </si>
-  <si>
-    <t>0.0382,0.0009,0.9736,0.0030</t>
-  </si>
-  <si>
-    <t>0.6433,0.0246,0.3542,0.0207</t>
-  </si>
-  <si>
-    <t>0.4951,0.0034,0.7818,0.0009</t>
-  </si>
-  <si>
-    <t>0.0520,0.0021,0.9560,0.0071</t>
-  </si>
-  <si>
-    <t>0.0069,0.0021,0.9777,0.0246</t>
-  </si>
-  <si>
-    <t>0.2596,0.7881,0.0091,0.0023</t>
-  </si>
-  <si>
-    <t>0.1120,0.7702,0.1350,0.0011</t>
-  </si>
-  <si>
-    <t>0.0049,0.0176,0.9919,0.0022</t>
-  </si>
-  <si>
-    <t>0.0065,0.9790,0.0350,0.0002</t>
-  </si>
-  <si>
-    <t>0.6388,0.2736,0.1383,0.0250</t>
-  </si>
-  <si>
-    <t>0.1890,0.0920,0.8165,0.0089</t>
-  </si>
-  <si>
-    <t>0.8808,0.1822,0.0041,0.0002</t>
-  </si>
-  <si>
-    <t>0.0454,0.8452,0.4050,0.0018</t>
-  </si>
-  <si>
-    <t>0.0127,0.7984,0.5949,0.0011</t>
-  </si>
-  <si>
-    <t>0.0143,0.1375,0.9545,0.0134</t>
-  </si>
-  <si>
-    <t>0.0297,0.0259,0.9385,0.0211</t>
-  </si>
-  <si>
-    <t>0.0748,0.0169,0.8300,0.1051</t>
-  </si>
-  <si>
-    <t>0.0543,0.2990,0.8460,0.0057</t>
-  </si>
-  <si>
-    <t>0.0213,0.9414,0.0487,0.0009</t>
-  </si>
-  <si>
-    <t>0.0447,0.0768,0.9073,0.0065</t>
-  </si>
-  <si>
-    <t>0.0156,0.8272,0.0058,0.8969</t>
-  </si>
-  <si>
-    <t>0.0024,0.9904,0.0093,0.0008</t>
-  </si>
-  <si>
-    <t>0.0017,0.9883,0.0257,0.0018</t>
-  </si>
-  <si>
-    <t>0.0009,0.9944,0.0122,0.0007</t>
-  </si>
-  <si>
-    <t>0.0075,0.5152,0.8680,0.0017</t>
-  </si>
-  <si>
-    <t>0.0210,0.4098,0.8881,0.0005</t>
-  </si>
-  <si>
-    <t>0.0385,0.3373,0.8770,0.0026</t>
-  </si>
-  <si>
-    <t>0.1317,0.0054,0.9306,0.0008</t>
-  </si>
-  <si>
-    <t>0.0217,0.0261,0.9611,0.0094</t>
-  </si>
-  <si>
-    <t>0.0267,0.0680,0.9268,0.0014</t>
-  </si>
-  <si>
-    <t>0.8801,0.1716,0.0048,0.0005</t>
-  </si>
-  <si>
-    <t>0.9806,0.0163,0.0025,0.0008</t>
-  </si>
-  <si>
-    <t>0.9744,0.0179,0.0069,0.0011</t>
-  </si>
-  <si>
-    <t>0.0072,0.1015,0.9867,0.0010</t>
-  </si>
-  <si>
-    <t>0.9806,0.0211,0.0017,0.0002</t>
-  </si>
-  <si>
-    <t>0.9694,0.0503,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.7716,0.3158,0.0076,0.0008</t>
-  </si>
-  <si>
-    <t>0.0070,0.8887,0.5952,0.0003</t>
-  </si>
-  <si>
-    <t>0.0063,0.3217,0.9592,0.0016</t>
-  </si>
-  <si>
-    <t>0.0268,0.1615,0.8948,0.0122</t>
-  </si>
-  <si>
-    <t>0.0024,0.9233,0.8005,0.0005</t>
-  </si>
-  <si>
-    <t>0.0128,0.0096,0.9735,0.0144</t>
-  </si>
-  <si>
-    <t>0.0499,0.9240,0.0098,0.0000</t>
-  </si>
-  <si>
-    <t>0.0257,0.9826,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.9080,0.0172,0.1013,0.0037</t>
-  </si>
-  <si>
-    <t>0.2218,0.7292,0.1084,0.0023</t>
-  </si>
-  <si>
-    <t>0.1013,0.4959,0.3642,0.0011</t>
-  </si>
-  <si>
-    <t>0.0039,0.8940,0.6871,0.0007</t>
-  </si>
-  <si>
-    <t>0.0011,0.8861,0.8489,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.9890,0.0671,0.0000</t>
-  </si>
-  <si>
-    <t>0.0019,0.9670,0.4851,0.0001</t>
-  </si>
-  <si>
-    <t>0.1919,0.0016,0.0128,0.8933</t>
-  </si>
-  <si>
-    <t>0.0035,0.0202,0.0001,0.9974</t>
-  </si>
-  <si>
-    <t>0.0260,0.0020,0.0002,0.9941</t>
-  </si>
-  <si>
-    <t>0.0573,0.0011,0.0015,0.9795</t>
-  </si>
-  <si>
-    <t>0.0182,0.0046,0.0036,0.9894</t>
-  </si>
-  <si>
-    <t>0.0054,0.0055,0.0006,0.9968</t>
-  </si>
-  <si>
-    <t>0.0019,0.9362,0.6960,0.0003</t>
-  </si>
-  <si>
-    <t>0.0334,0.4187,0.8856,0.0037</t>
-  </si>
-  <si>
-    <t>0.0225,0.7851,0.4942,0.0034</t>
-  </si>
-  <si>
-    <t>0.0011,0.9004,0.8335,0.0007</t>
-  </si>
-  <si>
-    <t>0.0077,0.8934,0.6436,0.0009</t>
-  </si>
-  <si>
-    <t>0.0093,0.8179,0.6838,0.0013</t>
-  </si>
-  <si>
-    <t>0.9887,0.0170,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9842,0.0177,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.9799,0.0233,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9882,0.0061,0.0005,0.0009</t>
-  </si>
-  <si>
-    <t>0.9801,0.0174,0.0016,0.0007</t>
-  </si>
-  <si>
-    <t>0.9945,0.0056,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9938,0.0056,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9845,0.0180,0.0018,0.0002</t>
-  </si>
-  <si>
-    <t>0.9949,0.0022,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9966,0.0035,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9970,0.0022,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9908,0.0092,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9895,0.0112,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9988,0.0007,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9973,0.0007,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.1031,0.0055,0.9538,0.0012</t>
-  </si>
-  <si>
-    <t>0.0495,0.1051,0.9159,0.0016</t>
-  </si>
-  <si>
-    <t>0.8778,0.0091,0.1394,0.0029</t>
-  </si>
-  <si>
-    <t>0.0705,0.0533,0.8728,0.0166</t>
-  </si>
-  <si>
-    <t>0.0150,0.9851,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.0278,0.9761,0.0018,0.0002</t>
-  </si>
-  <si>
-    <t>0.1240,0.9204,0.0030,0.0003</t>
-  </si>
-  <si>
-    <t>0.1498,0.8902,0.0024,0.0011</t>
-  </si>
-  <si>
-    <t>0.0885,0.9225,0.0042,0.0003</t>
-  </si>
-  <si>
-    <t>0.0273,0.9784,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.1955,0.8611,0.0037,0.0010</t>
-  </si>
-  <si>
-    <t>0.7921,0.0551,0.1403,0.0051</t>
-  </si>
-  <si>
-    <t>0.2192,0.0105,0.8079,0.0270</t>
-  </si>
-  <si>
-    <t>0.3743,0.1799,0.3706,0.0056</t>
-  </si>
-  <si>
-    <t>0.0768,0.8907,0.0325,0.0017</t>
-  </si>
-  <si>
-    <t>0.2104,0.0248,0.0539,0.8228</t>
-  </si>
-  <si>
-    <t>0.0031,0.9900,0.0245,0.0001</t>
-  </si>
-  <si>
-    <t>0.0052,0.9862,0.0077,0.0006</t>
-  </si>
-  <si>
-    <t>0.0120,0.9609,0.0023,0.1223</t>
-  </si>
-  <si>
-    <t>0.0005,0.9116,0.9697,0.0001</t>
-  </si>
-  <si>
-    <t>0.0036,0.9920,0.0258,0.0000</t>
-  </si>
-  <si>
-    <t>0.8646,0.1645,0.0112,0.0002</t>
-  </si>
-  <si>
-    <t>0.7907,0.2487,0.0168,0.0006</t>
-  </si>
-  <si>
-    <t>0.9222,0.1012,0.0036,0.0005</t>
-  </si>
-  <si>
-    <t>0.9804,0.0179,0.0035,0.0005</t>
-  </si>
-  <si>
-    <t>0.9831,0.0099,0.0022,0.0009</t>
-  </si>
-  <si>
-    <t>0.9896,0.0089,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.9917,0.0036,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9623,0.0263,0.0122,0.0011</t>
-  </si>
-  <si>
-    <t>0.9920,0.0054,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.9922,0.0037,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.0227,0.3756,0.8813,0.0016</t>
-  </si>
-  <si>
-    <t>0.0099,0.7039,0.8012,0.0017</t>
-  </si>
-  <si>
-    <t>0.0817,0.1550,0.8536,0.0049</t>
-  </si>
-  <si>
-    <t>0.1050,0.0318,0.8863,0.0071</t>
-  </si>
-  <si>
-    <t>0.8306,0.1288,0.0279,0.0066</t>
-  </si>
-  <si>
-    <t>0.6666,0.0657,0.2341,0.0005</t>
-  </si>
-  <si>
-    <t>0.4483,0.0024,0.8188,0.0016</t>
-  </si>
-  <si>
-    <t>0.3638,0.5332,0.0662,0.0018</t>
-  </si>
-  <si>
-    <t>0.0457,0.0108,0.0040,0.9790</t>
-  </si>
-  <si>
-    <t>0.0003,0.0007,0.0009,0.9993</t>
-  </si>
-  <si>
-    <t>0.0171,0.0020,0.0040,0.9876</t>
-  </si>
-  <si>
-    <t>0.0072,0.0039,0.0003,0.9970</t>
-  </si>
-  <si>
-    <t>0.0068,0.9288,0.5352,0.0008</t>
-  </si>
-  <si>
-    <t>0.9466,0.0620,0.0040,0.0021</t>
-  </si>
-  <si>
-    <t>0.1335,0.9112,0.0036,0.0021</t>
-  </si>
-  <si>
-    <t>0.9827,0.0105,0.0008,0.0015</t>
-  </si>
-  <si>
-    <t>0.5260,0.5468,0.0182,0.0018</t>
-  </si>
-  <si>
-    <t>0.9814,0.0074,0.0043,0.0011</t>
-  </si>
-  <si>
-    <t>0.6193,0.0106,0.0608,0.4028</t>
-  </si>
-  <si>
-    <t>0.9566,0.0393,0.0034,0.0038</t>
-  </si>
-  <si>
-    <t>0.0162,0.0419,0.9385,0.0522</t>
-  </si>
-  <si>
-    <t>0.9185,0.0040,0.0047,0.0759</t>
-  </si>
-  <si>
-    <t>0.9456,0.0021,0.0137,0.0198</t>
-  </si>
-  <si>
-    <t>0.3869,0.6129,0.0480,0.0033</t>
-  </si>
-  <si>
-    <t>0.9530,0.0340,0.0081,0.0003</t>
-  </si>
-  <si>
-    <t>0.8210,0.1375,0.0450,0.0014</t>
-  </si>
-  <si>
-    <t>0.4036,0.5884,0.0235,0.0126</t>
-  </si>
-  <si>
-    <t>0.7828,0.1630,0.0438,0.0005</t>
-  </si>
-  <si>
-    <t>0.9066,0.0701,0.0169,0.0004</t>
-  </si>
-  <si>
-    <t>0.9957,0.0015,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9886,0.0145,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9949,0.0013,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.9867,0.0037,0.0010,0.0026</t>
-  </si>
-  <si>
-    <t>0.9870,0.0077,0.0020,0.0008</t>
-  </si>
-  <si>
-    <t>0.9874,0.0116,0.0014,0.0003</t>
-  </si>
-  <si>
-    <t>0.9941,0.0029,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9935,0.0049,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.4709,0.6496,0.0016,0.0009</t>
-  </si>
-  <si>
-    <t>0.2064,0.8741,0.0028,0.0003</t>
-  </si>
-  <si>
-    <t>0.5908,0.5517,0.0052,0.0005</t>
-  </si>
-  <si>
-    <t>0.1980,0.2140,0.8063,0.0036</t>
-  </si>
-  <si>
-    <t>0.9667,0.0395,0.0026,0.0005</t>
-  </si>
-  <si>
-    <t>0.8864,0.0741,0.0466,0.0081</t>
-  </si>
-  <si>
-    <t>0.9781,0.0198,0.0035,0.0002</t>
-  </si>
-  <si>
-    <t>0.8342,0.1538,0.0289,0.0006</t>
-  </si>
-  <si>
-    <t>0.0230,0.0303,0.9865,0.0008</t>
-  </si>
-  <si>
-    <t>0.9313,0.0664,0.0111,0.0017</t>
-  </si>
-  <si>
-    <t>0.0170,0.0055,0.9877,0.0006</t>
-  </si>
-  <si>
-    <t>0.0041,0.0913,0.9800,0.0034</t>
-  </si>
-  <si>
-    <t>0.0379,0.0200,0.9646,0.0026</t>
-  </si>
-  <si>
-    <t>0.0280,0.1136,0.9293,0.0009</t>
-  </si>
-  <si>
-    <t>0.0703,0.0520,0.9195,0.0002</t>
-  </si>
-  <si>
-    <t>0.0214,0.0016,0.9906,0.0002</t>
-  </si>
-  <si>
-    <t>0.0083,0.0718,0.9750,0.0027</t>
-  </si>
-  <si>
-    <t>0.3322,0.0304,0.7531,0.0085</t>
-  </si>
-  <si>
-    <t>0.7488,0.0029,0.5084,0.0007</t>
-  </si>
-  <si>
-    <t>0.3939,0.3072,0.2492,0.0045</t>
-  </si>
-  <si>
-    <t>0.1340,0.6682,0.2660,0.0052</t>
-  </si>
-  <si>
-    <t>0.3061,0.4037,0.1759,0.0016</t>
-  </si>
-  <si>
-    <t>0.6974,0.1216,0.1465,0.0014</t>
-  </si>
-  <si>
-    <t>0.5412,0.2462,0.2169,0.0081</t>
-  </si>
-  <si>
-    <t>0.1350,0.0486,0.8390,0.0114</t>
-  </si>
-  <si>
-    <t>0.2971,0.7954,0.0058,0.0008</t>
-  </si>
-  <si>
-    <t>0.2869,0.8339,0.0025,0.0004</t>
-  </si>
-  <si>
-    <t>0.5304,0.6126,0.0080,0.0008</t>
-  </si>
-  <si>
-    <t>0.7978,0.3008,0.0024,0.0015</t>
-  </si>
-  <si>
-    <t>0.4414,0.7336,0.0035,0.0006</t>
-  </si>
-  <si>
-    <t>0.3877,0.3495,0.2767,0.0470</t>
-  </si>
-  <si>
-    <t>0.8996,0.0093,0.1430,0.0007</t>
-  </si>
-  <si>
-    <t>0.8423,0.0141,0.0880,0.0183</t>
-  </si>
-  <si>
-    <t>0.8441,0.0042,0.2890,0.0014</t>
-  </si>
-  <si>
-    <t>0.8287,0.0229,0.1558,0.0025</t>
-  </si>
-  <si>
-    <t>0.0565,0.0057,0.9218,0.0356</t>
-  </si>
-  <si>
-    <t>0.0621,0.2964,0.6665,0.0986</t>
-  </si>
-  <si>
-    <t>0.0667,0.0285,0.8914,0.0437</t>
-  </si>
-  <si>
-    <t>0.1730,0.0756,0.7715,0.0699</t>
-  </si>
-  <si>
-    <t>0.1066,0.0684,0.8118,0.0194</t>
-  </si>
-  <si>
-    <t>0.9823,0.0222,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9981,0.0009,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9908,0.0152,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9956,0.0030,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9805,0.0152,0.0044,0.0003</t>
-  </si>
-  <si>
-    <t>0.9975,0.0017,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9968,0.0024,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9659,0.0407,0.0015,0.0008</t>
-  </si>
-  <si>
-    <t>0.1505,0.0085,0.9340,0.0020</t>
-  </si>
-  <si>
-    <t>0.0506,0.7017,0.5215,0.0025</t>
-  </si>
-  <si>
-    <t>0.9062,0.0152,0.0523,0.0185</t>
-  </si>
-  <si>
-    <t>0.0569,0.0034,0.9552,0.0034</t>
-  </si>
-  <si>
-    <t>0.0018,0.0078,0.9873,0.0136</t>
-  </si>
-  <si>
-    <t>0.0496,0.2287,0.7670,0.0081</t>
-  </si>
-  <si>
-    <t>0.0012,0.0049,0.9961,0.0018</t>
-  </si>
-  <si>
-    <t>0.0342,0.0331,0.9295,0.0040</t>
-  </si>
-  <si>
-    <t>0.0036,0.0046,0.9953,0.0009</t>
-  </si>
-  <si>
-    <t>0.0066,0.0519,0.9706,0.0027</t>
-  </si>
-  <si>
-    <t>0.2436,0.0924,0.7030,0.0084</t>
-  </si>
-  <si>
-    <t>0.7680,0.0068,0.3705,0.0044</t>
-  </si>
-  <si>
-    <t>0.7394,0.0015,0.2442,0.0205</t>
-  </si>
-  <si>
-    <t>0.8857,0.0082,0.1554,0.0035</t>
-  </si>
-  <si>
-    <t>0.9911,0.0112,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9974,0.0013,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9879,0.0214,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9704,0.0427,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0007,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9922,0.0090,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9826,0.0137,0.0050,0.0002</t>
-  </si>
-  <si>
-    <t>0.9867,0.0102,0.0012,0.0005</t>
-  </si>
-  <si>
-    <t>0.0828,0.0177,0.9243,0.0015</t>
-  </si>
-  <si>
-    <t>0.0019,0.0429,0.9892,0.0016</t>
-  </si>
-  <si>
-    <t>0.0086,0.2026,0.9602,0.0003</t>
-  </si>
-  <si>
-    <t>0.2016,0.0310,0.8137,0.0039</t>
-  </si>
-  <si>
-    <t>0.0357,0.0191,0.9686,0.0032</t>
-  </si>
-  <si>
-    <t>0.2069,0.0191,0.3792,0.5300</t>
-  </si>
-  <si>
-    <t>0.0554,0.1724,0.8533,0.0088</t>
-  </si>
-  <si>
-    <t>0.1703,0.1037,0.7123,0.0862</t>
-  </si>
-  <si>
-    <t>0.8203,0.0006,0.0244,0.1269</t>
-  </si>
-  <si>
-    <t>0.0310,0.0716,0.0058,0.9783</t>
-  </si>
-  <si>
-    <t>0.0140,0.0052,0.0001,0.9956</t>
-  </si>
-  <si>
-    <t>0.0156,0.0016,0.0002,0.9954</t>
-  </si>
-  <si>
-    <t>0.0046,0.0002,0.0001,0.9985</t>
-  </si>
-  <si>
-    <t>0.7168,0.0456,0.0442,0.1819</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.8691,0.0421,0.0443,0.0253</t>
+  </si>
+  <si>
+    <t>0.0200,0.0036,0.0004,0.9941</t>
+  </si>
+  <si>
+    <t>0.6919,0.0158,0.0035,0.2904</t>
+  </si>
+  <si>
+    <t>0.0833,0.0028,0.0048,0.9701</t>
+  </si>
+  <si>
+    <t>0.9985,0.0017,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9945,0.0053,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9933,0.0048,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9875,0.0262,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9562,0.0581,0.0035,0.0004</t>
+  </si>
+  <si>
+    <t>0.9979,0.0016,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.2408,0.6126,0.0896,0.0721</t>
+  </si>
+  <si>
+    <t>0.3682,0.0453,0.7090,0.0024</t>
+  </si>
+  <si>
+    <t>0.2976,0.0570,0.6633,0.0004</t>
+  </si>
+  <si>
+    <t>0.0800,0.0113,0.9567,0.0012</t>
+  </si>
+  <si>
+    <t>0.5351,0.0907,0.5314,0.0093</t>
+  </si>
+  <si>
+    <t>0.0023,0.9943,0.0022,0.0002</t>
+  </si>
+  <si>
+    <t>0.0105,0.9842,0.0035,0.0005</t>
+  </si>
+  <si>
+    <t>0.1076,0.9043,0.0133,0.0004</t>
+  </si>
+  <si>
+    <t>0.0099,0.9856,0.0047,0.0003</t>
+  </si>
+  <si>
+    <t>0.0045,0.9887,0.0086,0.0005</t>
+  </si>
+  <si>
+    <t>0.2528,0.0099,0.8214,0.0102</t>
+  </si>
+  <si>
+    <t>0.5495,0.0260,0.4961,0.0118</t>
+  </si>
+  <si>
+    <t>0.0232,0.0259,0.9769,0.0002</t>
+  </si>
+  <si>
+    <t>0.0661,0.0699,0.8620,0.0049</t>
+  </si>
+  <si>
+    <t>0.0592,0.0175,0.9615,0.0031</t>
+  </si>
+  <si>
+    <t>0.1200,0.0290,0.8873,0.0024</t>
+  </si>
+  <si>
+    <t>0.0040,0.0059,0.9860,0.0141</t>
+  </si>
+  <si>
+    <t>0.2110,0.8087,0.0219,0.0011</t>
+  </si>
+  <si>
+    <t>0.3556,0.1074,0.6467,0.0051</t>
+  </si>
+  <si>
+    <t>0.0123,0.0433,0.9751,0.0055</t>
+  </si>
+  <si>
+    <t>0.0051,0.9282,0.2943,0.0002</t>
+  </si>
+  <si>
+    <t>0.8769,0.0777,0.0443,0.0020</t>
+  </si>
+  <si>
+    <t>0.7815,0.2102,0.0450,0.0051</t>
+  </si>
+  <si>
+    <t>0.7882,0.4129,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.3393,0.5852,0.1486,0.0220</t>
+  </si>
+  <si>
+    <t>0.0407,0.3708,0.8065,0.0093</t>
+  </si>
+  <si>
+    <t>0.0267,0.0801,0.9577,0.0088</t>
+  </si>
+  <si>
+    <t>0.0488,0.5352,0.3860,0.0961</t>
+  </si>
+  <si>
+    <t>0.3512,0.0050,0.5506,0.0658</t>
+  </si>
+  <si>
+    <t>0.0464,0.2133,0.8883,0.0022</t>
+  </si>
+  <si>
+    <t>0.0135,0.9574,0.0471,0.0013</t>
+  </si>
+  <si>
+    <t>0.0240,0.0476,0.9344,0.0145</t>
+  </si>
+  <si>
+    <t>0.1379,0.2214,0.0305,0.8692</t>
+  </si>
+  <si>
+    <t>0.0018,0.9921,0.0080,0.0010</t>
+  </si>
+  <si>
+    <t>0.0025,0.9887,0.0194,0.0005</t>
+  </si>
+  <si>
+    <t>0.0028,0.9900,0.0153,0.0003</t>
+  </si>
+  <si>
+    <t>0.0540,0.5719,0.6291,0.0135</t>
+  </si>
+  <si>
+    <t>0.0125,0.0840,0.9736,0.0013</t>
+  </si>
+  <si>
+    <t>0.0487,0.0071,0.9353,0.0239</t>
+  </si>
+  <si>
+    <t>0.2573,0.0015,0.9099,0.0006</t>
+  </si>
+  <si>
+    <t>0.0672,0.0107,0.9580,0.0009</t>
+  </si>
+  <si>
+    <t>0.0080,0.2593,0.9525,0.0003</t>
+  </si>
+  <si>
+    <t>0.9665,0.0591,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.9392,0.0536,0.0168,0.0011</t>
+  </si>
+  <si>
+    <t>0.9614,0.0342,0.0049,0.0020</t>
+  </si>
+  <si>
+    <t>0.0569,0.1034,0.9377,0.0079</t>
+  </si>
+  <si>
+    <t>0.9685,0.0388,0.0028,0.0003</t>
+  </si>
+  <si>
+    <t>0.9694,0.0433,0.0016,0.0002</t>
+  </si>
+  <si>
+    <t>0.9876,0.0123,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.0038,0.8148,0.9279,0.0005</t>
+  </si>
+  <si>
+    <t>0.0027,0.2969,0.9673,0.0005</t>
+  </si>
+  <si>
+    <t>0.0247,0.1739,0.9059,0.0134</t>
+  </si>
+  <si>
+    <t>0.0037,0.7986,0.9124,0.0006</t>
+  </si>
+  <si>
+    <t>0.0644,0.0143,0.9569,0.0026</t>
+  </si>
+  <si>
+    <t>0.0099,0.9722,0.0318,0.0000</t>
+  </si>
+  <si>
+    <t>0.0203,0.9843,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.5802,0.0818,0.4455,0.0027</t>
+  </si>
+  <si>
+    <t>0.6190,0.0717,0.4868,0.0025</t>
+  </si>
+  <si>
+    <t>0.0181,0.0571,0.9683,0.0009</t>
+  </si>
+  <si>
+    <t>0.0160,0.8942,0.2668,0.0001</t>
+  </si>
+  <si>
+    <t>0.0047,0.8711,0.7010,0.0003</t>
+  </si>
+  <si>
+    <t>0.0015,0.9729,0.3128,0.0004</t>
+  </si>
+  <si>
+    <t>0.0025,0.9404,0.7588,0.0009</t>
+  </si>
+  <si>
+    <t>0.0844,0.0040,0.0237,0.9401</t>
+  </si>
+  <si>
+    <t>0.0040,0.0081,0.0001,0.9980</t>
+  </si>
+  <si>
+    <t>0.0049,0.0009,0.0004,0.9973</t>
+  </si>
+  <si>
+    <t>0.0847,0.0075,0.0019,0.9708</t>
+  </si>
+  <si>
+    <t>0.0452,0.0275,0.0074,0.9740</t>
+  </si>
+  <si>
+    <t>0.0080,0.0161,0.0005,0.9951</t>
+  </si>
+  <si>
+    <t>0.0015,0.9804,0.3278,0.0003</t>
+  </si>
+  <si>
+    <t>0.0048,0.7992,0.8933,0.0007</t>
+  </si>
+  <si>
+    <t>0.0322,0.6751,0.5961,0.0074</t>
+  </si>
+  <si>
+    <t>0.0090,0.6116,0.8994,0.0023</t>
+  </si>
+  <si>
+    <t>0.0015,0.9427,0.7108,0.0002</t>
+  </si>
+  <si>
+    <t>0.0020,0.9521,0.5020,0.0001</t>
+  </si>
+  <si>
+    <t>0.9960,0.0027,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9775,0.0253,0.0015,0.0004</t>
+  </si>
+  <si>
+    <t>0.9940,0.0056,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9977,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9647,0.0391,0.0036,0.0003</t>
+  </si>
+  <si>
+    <t>0.9982,0.0006,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9870,0.0109,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.9915,0.0120,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9940,0.0062,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9986,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9931,0.0020,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9944,0.0041,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9969,0.0018,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9989,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0173,0.0028,0.9758,0.0085</t>
+  </si>
+  <si>
+    <t>0.1636,0.0061,0.9244,0.0014</t>
+  </si>
+  <si>
+    <t>0.7621,0.0240,0.2122,0.0292</t>
+  </si>
+  <si>
+    <t>0.3263,0.0218,0.7643,0.0025</t>
+  </si>
+  <si>
+    <t>0.0394,0.9661,0.0040,0.0000</t>
+  </si>
+  <si>
+    <t>0.0534,0.9620,0.0018,0.0002</t>
+  </si>
+  <si>
+    <t>0.1545,0.8757,0.0034,0.0012</t>
+  </si>
+  <si>
+    <t>0.1643,0.8550,0.0131,0.0007</t>
+  </si>
+  <si>
+    <t>0.0172,0.9845,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.0081,0.9916,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.5102,0.6921,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.1927,0.7723,0.0419,0.0051</t>
+  </si>
+  <si>
+    <t>0.4834,0.0081,0.6728,0.0139</t>
+  </si>
+  <si>
+    <t>0.3696,0.3232,0.3247,0.0441</t>
+  </si>
+  <si>
+    <t>0.3909,0.1065,0.5387,0.0129</t>
+  </si>
+  <si>
+    <t>0.1714,0.1001,0.0226,0.8457</t>
+  </si>
+  <si>
+    <t>0.0014,0.9937,0.0109,0.0003</t>
+  </si>
+  <si>
+    <t>0.0020,0.9923,0.0070,0.0003</t>
+  </si>
+  <si>
+    <t>0.0494,0.8822,0.0682,0.0497</t>
+  </si>
+  <si>
+    <t>0.0046,0.9500,0.4885,0.0014</t>
+  </si>
+  <si>
+    <t>0.0058,0.9855,0.0491,0.0001</t>
+  </si>
+  <si>
+    <t>0.4819,0.5354,0.0226,0.0003</t>
+  </si>
+  <si>
+    <t>0.4154,0.6521,0.0192,0.0004</t>
+  </si>
+  <si>
+    <t>0.9694,0.0287,0.0060,0.0005</t>
+  </si>
+  <si>
+    <t>0.9923,0.0017,0.0008,0.0013</t>
+  </si>
+  <si>
+    <t>0.9935,0.0017,0.0007,0.0010</t>
+  </si>
+  <si>
+    <t>0.9766,0.0257,0.0016,0.0008</t>
+  </si>
+  <si>
+    <t>0.9967,0.0016,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9790,0.0078,0.0023,0.0040</t>
+  </si>
+  <si>
+    <t>0.9771,0.0158,0.0028,0.0013</t>
+  </si>
+  <si>
+    <t>0.9825,0.0058,0.0094,0.0007</t>
+  </si>
+  <si>
+    <t>0.0031,0.7391,0.9047,0.0013</t>
+  </si>
+  <si>
+    <t>0.0528,0.5955,0.4744,0.0006</t>
+  </si>
+  <si>
+    <t>0.0225,0.0866,0.9563,0.0035</t>
+  </si>
+  <si>
+    <t>0.0170,0.5927,0.5827,0.0003</t>
+  </si>
+  <si>
+    <t>0.7862,0.1117,0.0905,0.0261</t>
+  </si>
+  <si>
+    <t>0.7317,0.1537,0.0603,0.0068</t>
+  </si>
+  <si>
+    <t>0.1570,0.0015,0.8407,0.0447</t>
+  </si>
+  <si>
+    <t>0.4175,0.0966,0.5394,0.0060</t>
+  </si>
+  <si>
+    <t>0.0634,0.0024,0.0006,0.9839</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.0002,0.9996</t>
+  </si>
+  <si>
+    <t>0.0212,0.0032,0.0010,0.9914</t>
+  </si>
+  <si>
+    <t>0.0187,0.0073,0.0013,0.9920</t>
+  </si>
+  <si>
+    <t>0.0007,0.9815,0.1890,0.0009</t>
+  </si>
+  <si>
+    <t>0.9528,0.0419,0.0076,0.0006</t>
+  </si>
+  <si>
+    <t>0.1872,0.8388,0.0034,0.0158</t>
+  </si>
+  <si>
+    <t>0.9910,0.0024,0.0008,0.0016</t>
+  </si>
+  <si>
+    <t>0.5306,0.5897,0.0108,0.0009</t>
+  </si>
+  <si>
+    <t>0.9860,0.0045,0.0045,0.0013</t>
+  </si>
+  <si>
+    <t>0.2861,0.0054,0.0115,0.8226</t>
+  </si>
+  <si>
+    <t>0.9723,0.0187,0.0016,0.0038</t>
+  </si>
+  <si>
+    <t>0.0447,0.0822,0.8929,0.0586</t>
+  </si>
+  <si>
+    <t>0.6535,0.0015,0.0065,0.4960</t>
+  </si>
+  <si>
+    <t>0.9569,0.0010,0.0047,0.0238</t>
+  </si>
+  <si>
+    <t>0.4572,0.5705,0.0215,0.0068</t>
+  </si>
+  <si>
+    <t>0.9710,0.0193,0.0048,0.0005</t>
+  </si>
+  <si>
+    <t>0.8165,0.0850,0.1087,0.0010</t>
+  </si>
+  <si>
+    <t>0.4029,0.5285,0.0564,0.0075</t>
+  </si>
+  <si>
+    <t>0.3460,0.6809,0.0219,0.0006</t>
+  </si>
+  <si>
+    <t>0.6353,0.4174,0.0167,0.0020</t>
+  </si>
+  <si>
+    <t>0.9862,0.0099,0.0031,0.0003</t>
+  </si>
+  <si>
+    <t>0.9645,0.0516,0.0014,0.0006</t>
+  </si>
+  <si>
+    <t>0.9970,0.0011,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9885,0.0092,0.0009,0.0008</t>
+  </si>
+  <si>
+    <t>0.9961,0.0014,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9868,0.0105,0.0015,0.0005</t>
+  </si>
+  <si>
+    <t>0.9967,0.0008,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9947,0.0041,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.6546,0.4740,0.0069,0.0022</t>
+  </si>
+  <si>
+    <t>0.6774,0.4737,0.0053,0.0011</t>
+  </si>
+  <si>
+    <t>0.5378,0.5909,0.0070,0.0007</t>
+  </si>
+  <si>
+    <t>0.5207,0.3870,0.1588,0.0070</t>
+  </si>
+  <si>
+    <t>0.9865,0.0117,0.0018,0.0004</t>
+  </si>
+  <si>
+    <t>0.9743,0.0190,0.0043,0.0017</t>
+  </si>
+  <si>
+    <t>0.9623,0.0332,0.0055,0.0004</t>
+  </si>
+  <si>
+    <t>0.8936,0.1699,0.0020,0.0005</t>
+  </si>
+  <si>
+    <t>0.0126,0.0584,0.9867,0.0012</t>
+  </si>
+  <si>
+    <t>0.9295,0.0761,0.0090,0.0015</t>
+  </si>
+  <si>
+    <t>0.0281,0.0057,0.9841,0.0002</t>
+  </si>
+  <si>
+    <t>0.0045,0.0485,0.9879,0.0005</t>
+  </si>
+  <si>
+    <t>0.0474,0.0089,0.9647,0.0021</t>
+  </si>
+  <si>
+    <t>0.0090,0.2469,0.9532,0.0017</t>
+  </si>
+  <si>
+    <t>0.0287,0.0332,0.9670,0.0009</t>
+  </si>
+  <si>
+    <t>0.0351,0.0130,0.9658,0.0003</t>
+  </si>
+  <si>
+    <t>0.0254,0.1638,0.9044,0.0004</t>
+  </si>
+  <si>
+    <t>0.0415,0.0202,0.9555,0.0061</t>
+  </si>
+  <si>
+    <t>0.0746,0.0690,0.8975,0.0005</t>
+  </si>
+  <si>
+    <t>0.5390,0.1019,0.4716,0.0114</t>
+  </si>
+  <si>
+    <t>0.1924,0.1180,0.7027,0.0007</t>
+  </si>
+  <si>
+    <t>0.1273,0.7973,0.0792,0.0020</t>
+  </si>
+  <si>
+    <t>0.4389,0.3447,0.1572,0.0044</t>
+  </si>
+  <si>
+    <t>0.5792,0.2667,0.1420,0.0217</t>
+  </si>
+  <si>
+    <t>0.3564,0.4854,0.2002,0.0353</t>
+  </si>
+  <si>
+    <t>0.5698,0.6455,0.0014,0.0004</t>
+  </si>
+  <si>
+    <t>0.5110,0.6519,0.0036,0.0005</t>
+  </si>
+  <si>
+    <t>0.8481,0.2430,0.0040,0.0004</t>
+  </si>
+  <si>
+    <t>0.8585,0.2705,0.0015,0.0006</t>
+  </si>
+  <si>
+    <t>0.6875,0.4594,0.0057,0.0010</t>
+  </si>
+  <si>
+    <t>0.1692,0.7340,0.1105,0.0073</t>
+  </si>
+  <si>
+    <t>0.8176,0.0145,0.2874,0.0011</t>
+  </si>
+  <si>
+    <t>0.8181,0.0086,0.1066,0.0256</t>
+  </si>
+  <si>
+    <t>0.5279,0.0102,0.5909,0.0096</t>
+  </si>
+  <si>
+    <t>0.7411,0.0226,0.0638,0.1111</t>
+  </si>
+  <si>
+    <t>0.0266,0.0053,0.9636,0.0196</t>
+  </si>
+  <si>
+    <t>0.0454,0.4494,0.7079,0.0372</t>
+  </si>
+  <si>
+    <t>0.0098,0.0394,0.9739,0.0097</t>
+  </si>
+  <si>
+    <t>0.1475,0.0367,0.7374,0.1105</t>
+  </si>
+  <si>
+    <t>0.0097,0.8355,0.4733,0.0021</t>
+  </si>
+  <si>
+    <t>0.9968,0.0020,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9548,0.0654,0.0013,0.0007</t>
+  </si>
+  <si>
+    <t>0.9598,0.0474,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.9807,0.0323,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9653,0.0482,0.0018,0.0007</t>
+  </si>
+  <si>
+    <t>0.9928,0.0078,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9959,0.0031,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9970,0.0012,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.1317,0.0095,0.9225,0.0077</t>
+  </si>
+  <si>
+    <t>0.0892,0.3659,0.6927,0.0030</t>
+  </si>
+  <si>
+    <t>0.8686,0.0164,0.0974,0.0096</t>
+  </si>
+  <si>
+    <t>0.0147,0.0589,0.9607,0.0024</t>
+  </si>
+  <si>
+    <t>0.0045,0.0039,0.9835,0.0144</t>
+  </si>
+  <si>
+    <t>0.0243,0.0475,0.9507,0.0032</t>
+  </si>
+  <si>
+    <t>0.0092,0.0019,0.9921,0.0011</t>
+  </si>
+  <si>
+    <t>0.0504,0.1557,0.8197,0.0014</t>
+  </si>
+  <si>
+    <t>0.0057,0.0214,0.9908,0.0014</t>
+  </si>
+  <si>
+    <t>0.0107,0.0121,0.9767,0.0040</t>
+  </si>
+  <si>
+    <t>0.1289,0.1689,0.7309,0.0088</t>
+  </si>
+  <si>
+    <t>0.8576,0.0087,0.2137,0.0016</t>
+  </si>
+  <si>
+    <t>0.6344,0.0058,0.4716,0.0157</t>
+  </si>
+  <si>
+    <t>0.8357,0.0131,0.1897,0.0123</t>
+  </si>
+  <si>
+    <t>0.9932,0.0043,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9961,0.0031,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9965,0.0034,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9891,0.0140,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9884,0.0054,0.0015,0.0009</t>
+  </si>
+  <si>
+    <t>0.9900,0.0122,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9879,0.0114,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9844,0.0182,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.1006,0.2861,0.6514,0.0040</t>
+  </si>
+  <si>
+    <t>0.0190,0.0391,0.9659,0.0016</t>
+  </si>
+  <si>
+    <t>0.0103,0.0701,0.9708,0.0054</t>
+  </si>
+  <si>
+    <t>0.1617,0.1778,0.5906,0.0384</t>
+  </si>
+  <si>
+    <t>0.0553,0.0135,0.9461,0.0056</t>
+  </si>
+  <si>
+    <t>0.0545,0.0053,0.9189,0.0393</t>
+  </si>
+  <si>
+    <t>0.1615,0.0584,0.7731,0.0451</t>
+  </si>
+  <si>
+    <t>0.0241,0.1976,0.8708,0.0417</t>
+  </si>
+  <si>
+    <t>0.7788,0.0004,0.0017,0.3786</t>
+  </si>
+  <si>
+    <t>0.0519,0.0174,0.0211,0.9566</t>
+  </si>
+  <si>
+    <t>0.0210,0.0016,0.0005,0.9930</t>
+  </si>
+  <si>
+    <t>0.0108,0.0004,0.0040,0.9915</t>
+  </si>
+  <si>
+    <t>0.0060,0.0006,0.0004,0.9975</t>
+  </si>
+  <si>
+    <t>0.7424,0.0134,0.0090,0.2586</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1993,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,10 +2130,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,10 +2186,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2231,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2270,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,7 +2287,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,10 +2312,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2371,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2382,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2413,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,10 +2438,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2455,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2480,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,10 +2508,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2637,7 @@
         <v>263</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2819,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2917,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,10 +2928,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,10 +2942,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,10 +2956,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2973,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2987,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,10 +2998,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,10 +3096,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,10 +3110,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,10 +3124,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3141,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3155,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3169,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,10 +3544,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,10 +3558,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3586,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3600,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3617,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,10 +3670,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,10 +3698,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,10 +3712,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,10 +3838,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,10 +3852,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3869,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,10 +3880,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3925,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,10 +3936,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,10 +4006,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4037,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,10 +4062,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,10 +4090,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4163,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,7 +4205,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,10 +4216,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,10 +4356,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,10 +4370,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,10 +4384,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4398,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4597,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,7 +4625,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4636,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4650,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4664,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4681,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,10 +4692,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,10 +4706,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,10 +4720,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,10 +4734,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,10 +4762,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,10 +4776,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4807,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4818,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,10 +4902,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5042,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5199,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5406,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5451,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5521,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
